--- a/output/2025_A24_SECCION_E.xlsx
+++ b/output/2025_A24_SECCION_E.xlsx
@@ -838,7 +838,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+    <t>Hospital San Juan de Dios (Santiago)</t>
   </si>
   <si>
     <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
